--- a/data/Category_Country.xlsx
+++ b/data/Category_Country.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akash\bni_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DFBF50-FA37-4073-AEC3-4CF00B78054B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070D149A-8800-470B-B181-7799DE1CB869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="2130" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,108 +25,120 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="38">
   <si>
     <t>Country</t>
   </si>
   <si>
-    <t xml:space="preserve">India </t>
+    <t>Category1</t>
+  </si>
+  <si>
+    <t>Category2</t>
+  </si>
+  <si>
+    <t>Category3</t>
+  </si>
+  <si>
+    <t>Category4</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage (Chocolatier)</t>
+  </si>
+  <si>
+    <t>Category5</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage (Coffee House/Shop)</t>
+  </si>
+  <si>
+    <t>Category6</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage (Confectionery)</t>
+  </si>
+  <si>
+    <t>Category7</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage (Restaurant)</t>
+  </si>
+  <si>
+    <t>Category8</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage (Vegetable Supplier)</t>
+  </si>
+  <si>
+    <t>Category9</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage (Wine Merchant/Wine)</t>
+  </si>
+  <si>
+    <t>Category10</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage (Tea Merchant)</t>
+  </si>
+  <si>
+    <t>Category11</t>
+  </si>
+  <si>
+    <t>Category12</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverge(Tea Distribution)</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverages (Coffee Distribution)</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverages(Other)</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverages(Baker)</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverages(Food Service)</t>
+  </si>
+  <si>
+    <t>Kuwait</t>
+  </si>
+  <si>
+    <t>Dubai</t>
   </si>
   <si>
     <t>Food &amp; Beverage (Caterer)</t>
   </si>
   <si>
-    <t>Category1</t>
-  </si>
-  <si>
-    <t>Category2</t>
-  </si>
-  <si>
-    <t>Category3</t>
-  </si>
-  <si>
-    <t>Category4</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverage (Beverage Distributor)</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverage (Beverage Service)</t>
+    <t>Category13</t>
+  </si>
+  <si>
+    <t>Category14</t>
+  </si>
+  <si>
+    <t>Category15</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage (Beverage Services)</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage (Beverage Distribution)</t>
   </si>
   <si>
     <t>Food &amp; Beverage (Café)</t>
   </si>
   <si>
-    <t>Food &amp; Beverage (Chocolatier)</t>
-  </si>
-  <si>
-    <t>Category5</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverage (Coffee House/Shop)</t>
-  </si>
-  <si>
-    <t>Category6</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverage (Confectionery)</t>
-  </si>
-  <si>
-    <t>Category7</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverage (Restaurant)</t>
-  </si>
-  <si>
-    <t>Category8</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverage (Vegetable Supplier)</t>
-  </si>
-  <si>
-    <t>Category9</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverage (Wine Merchant/Wine)</t>
-  </si>
-  <si>
-    <t>Category10</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverage (Tea Merchant)</t>
-  </si>
-  <si>
-    <t>Category11</t>
-  </si>
-  <si>
-    <t>Category12</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverge(Tea Distribution)</t>
-  </si>
-  <si>
-    <t>Category13</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverages (Coffee Distribution)</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverages(Other)</t>
-  </si>
-  <si>
-    <t>Category14</t>
-  </si>
-  <si>
-    <t>Category15</t>
-  </si>
-  <si>
-    <t>Food &amp; Beverages(Baker)</t>
-  </si>
-  <si>
     <t>Category16</t>
   </si>
   <si>
-    <t>Food &amp; Beverages(Food Service)</t>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>Philipines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indoneasia </t>
   </si>
 </sst>
 </file>
@@ -188,26 +200,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{152C1C60-8B6B-404B-BA93-792100203AE2}" name="Table1" displayName="Table1" ref="A1:Q4" totalsRowShown="0">
-  <autoFilter ref="A1:Q4" xr:uid="{152C1C60-8B6B-404B-BA93-792100203AE2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{345A00DD-A82B-46EF-8723-467FA0BFFEE7}" name="Table1345" displayName="Table1345" ref="A1:Q3" totalsRowShown="0">
+  <autoFilter ref="A1:Q3" xr:uid="{152C1C60-8B6B-404B-BA93-792100203AE2}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{2F180D01-71E9-4EBD-BF38-AF20973CE19D}" name="Country"/>
-    <tableColumn id="2" xr3:uid="{2E1DB0AB-66E3-40D2-BF97-B582975A6DD2}" name="Category1"/>
-    <tableColumn id="3" xr3:uid="{B1291A07-9F59-4B61-AC22-31C9546A9BBA}" name="Category2"/>
-    <tableColumn id="4" xr3:uid="{6882CCFD-CC23-47FD-B5B0-3C2CDFBE73EA}" name="Category3"/>
-    <tableColumn id="5" xr3:uid="{BA2E1D11-3765-4A2B-A3F2-23BE05F049F9}" name="Category4"/>
-    <tableColumn id="6" xr3:uid="{3F91DD81-AE72-4C4D-96F7-61D6F0C037E0}" name="Category5"/>
-    <tableColumn id="7" xr3:uid="{80EF98F7-1413-4A1F-9E99-D4B9C1ECD96C}" name="Category6"/>
-    <tableColumn id="8" xr3:uid="{48355F9E-CB75-4415-B03B-1BB80A698372}" name="Category7"/>
-    <tableColumn id="9" xr3:uid="{3C5C28FB-6710-46BC-9BCC-6B8BC94AC65C}" name="Category8"/>
-    <tableColumn id="10" xr3:uid="{82392485-4294-4F31-A9CD-9E2EEB4D4F5D}" name="Category9"/>
-    <tableColumn id="11" xr3:uid="{03E79EEC-3D15-4772-B36A-9F2652728FE7}" name="Category10"/>
-    <tableColumn id="12" xr3:uid="{59C500D8-4D74-4BEE-B038-92FBCDBC2AA4}" name="Category11"/>
-    <tableColumn id="13" xr3:uid="{51F8C6BB-056F-4FDF-BD1D-EC689F913507}" name="Category12"/>
-    <tableColumn id="14" xr3:uid="{7B0429EE-31CB-4773-8728-87D49E5B22A8}" name="Category13"/>
-    <tableColumn id="15" xr3:uid="{86707682-E0BD-46BA-9194-D892F85A54D5}" name="Category14"/>
-    <tableColumn id="16" xr3:uid="{B3E7AE9B-88B0-4BFE-801F-C1DEFB055E61}" name="Category15"/>
-    <tableColumn id="17" xr3:uid="{1FF3507F-9934-4EB4-AFB1-A44D4879B1F7}" name="Category16"/>
+    <tableColumn id="1" xr3:uid="{9FF22D08-7B16-453E-8069-7FB6A9B49A15}" name="Country"/>
+    <tableColumn id="6" xr3:uid="{98105C52-84F3-46AC-9BFE-A0DF77181A4B}" name="Category1"/>
+    <tableColumn id="7" xr3:uid="{C69BC43F-DD89-42F2-961C-6A4D459AC253}" name="Category2"/>
+    <tableColumn id="8" xr3:uid="{79A0319E-D103-4782-9F14-F8E832BA55F1}" name="Category3"/>
+    <tableColumn id="9" xr3:uid="{F3CBC86D-F73D-48DC-9039-0D6D77A3BDCD}" name="Category4"/>
+    <tableColumn id="10" xr3:uid="{FCCE04E9-F294-46A5-B660-C85D9B38AEC2}" name="Category5"/>
+    <tableColumn id="11" xr3:uid="{39794040-B48F-4F76-A6D8-837F816C7A37}" name="Category6"/>
+    <tableColumn id="12" xr3:uid="{D9D6C93E-7642-40B7-83FC-BE13E1E802D0}" name="Category7"/>
+    <tableColumn id="13" xr3:uid="{09B5C6CB-FE16-469B-B5C1-138BA66595B8}" name="Category8"/>
+    <tableColumn id="14" xr3:uid="{6EAEDAB4-3689-43A1-A896-F308A7EE01CF}" name="Category9"/>
+    <tableColumn id="15" xr3:uid="{54C7E772-4BC2-418E-BB9D-0DCE4CC0BEC2}" name="Category10"/>
+    <tableColumn id="16" xr3:uid="{AEB8C45E-06B1-47E2-9519-38BBDA736008}" name="Category11"/>
+    <tableColumn id="17" xr3:uid="{34334146-C673-44EC-9421-CF2E6ACECA82}" name="Category12"/>
+    <tableColumn id="2" xr3:uid="{5FDAF00D-2180-4165-AEE6-6BD079A20039}" name="Category13"/>
+    <tableColumn id="3" xr3:uid="{6F5C20DF-EC59-44CF-8DB3-B77C77CFBD5B}" name="Category14"/>
+    <tableColumn id="4" xr3:uid="{30BCCB9D-99C6-4D77-9D67-A973B8857293}" name="Category15"/>
+    <tableColumn id="5" xr3:uid="{5C6F60AF-955E-4024-B00E-7EB43A818550}" name="Category16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -475,8 +487,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2A15AAC-573E-40D2-9AB3-453F46C15A99}">
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" customWidth="1"/>
@@ -493,8 +505,8 @@
     <col min="12" max="12" width="29.33203125" customWidth="1"/>
     <col min="13" max="13" width="30.33203125" customWidth="1"/>
     <col min="14" max="14" width="33.44140625" customWidth="1"/>
-    <col min="15" max="15" width="29.21875" customWidth="1"/>
-    <col min="16" max="16" width="22.88671875" customWidth="1"/>
+    <col min="15" max="15" width="38.6640625" customWidth="1"/>
+    <col min="16" max="16" width="42.109375" customWidth="1"/>
     <col min="17" max="17" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -503,43 +515,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
       <c r="G1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="K1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" t="s">
-        <v>24</v>
-      </c>
       <c r="N1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O1" t="s">
         <v>29</v>
@@ -548,59 +560,271 @@
         <v>30</v>
       </c>
       <c r="Q1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" t="s">
         <v>27</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" t="s">
         <v>33</v>
       </c>
     </row>
